--- a/public/modeles/Modele-Modules.xlsx
+++ b/public/modeles/Modele-Modules.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Configuration de votre CRM</t>
   </si>
@@ -50,10 +50,13 @@
     <t>Activé</t>
   </si>
   <si>
+    <t>Assistant commercial</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
     <t>Propositions commerciales</t>
-  </si>
-  <si>
-    <t>Oui</t>
   </si>
   <si>
     <t>Finances</t>
@@ -638,7 +641,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25"/>
